--- a/erp-server/erp-server-mrp/src/main/resources/excel/deliverySuggestError.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/deliverySuggestError.xlsx
@@ -1106,7 +1106,7 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
